--- a/tests/testthat/data/TestProjectExcelLegacy/Configurations/Applications.xlsx
+++ b/tests/testthat/data/TestProjectExcelLegacy/Configurations/Applications.xlsx
@@ -11,6 +11,32 @@
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
+</file>
+
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+  <si>
+    <t>Container Path</t>
+  </si>
+  <si>
+    <t>Parameter Name</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Units</t>
+  </si>
+  <si>
+    <t>Events|IV 250mg 10min|No formulation|Application_1|ProtocolSchemaItem</t>
+  </si>
+  <si>
+    <t>Dose</t>
+  </si>
+  <si>
+    <t>mg</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -354,46 +380,32 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" s="1" customFormat="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Container Path</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Parameter Name</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Value</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Units</t>
-        </is>
+    <row r="1" spans="1:4" s="1" customFormat="1">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Events|IV 250mg 10min|Application_1|ProtocolSchemaItem</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Dose</t>
-        </is>
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
       </c>
       <c r="C2">
         <v>250</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>mg</t>
-        </is>
+      <c r="D2" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
